--- a/silbido-master/Analisi_Giugno2014_88%_150ms.xlsx
+++ b/silbido-master/Analisi_Giugno2014_88%_150ms.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="257">
   <si>
     <t>file_name</t>
   </si>
@@ -418,6 +418,378 @@
   </si>
   <si>
     <t>2014-06-16 12:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_121000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 12:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_130000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 13:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_131000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 13:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_140000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 14:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_141000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 14:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_150000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 15:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_151000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 15:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_160000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 16:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_161000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 16:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_170000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 17:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_171000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 17:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_180000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 18:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_181000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 18:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_190000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 19:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_191000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 19:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_200000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 20:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_201000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 20:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_210000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 21:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_211000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 21:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_220000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 22:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_221000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 22:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_230000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 23:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140608_231000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-08 23:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_000000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 00:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_001000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 00:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_010000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 01:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_011000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 01:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_020000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 02:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_021000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 02:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_030000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 03:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_031000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 03:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_040000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 04:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_041000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 04:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_050000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 05:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_051000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 05:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_060000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 06:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_061000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 06:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_070000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 07:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_071000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 07:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_080000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 08:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_081000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 08:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_090000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 09:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_091000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 09:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_100000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 10:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_101000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 10:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_110000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 11:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_111000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 11:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_120000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 12:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_121000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 12:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_130000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 13:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_131000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 13:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_140000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 14:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_141000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 14:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_150000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 15:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_151000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 15:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_160000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 16:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_161000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 16:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_170000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 17:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_171000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 17:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_180000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 18:00:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_181000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 18:10:00</t>
+  </si>
+  <si>
+    <t>REC-B_20140609_190000.wav</t>
+  </si>
+  <si>
+    <t>2014-06-09 19:00:00</t>
   </si>
 </sst>
 </file>
@@ -732,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
@@ -3361,6 +3733,1990 @@
         <v>0</v>
       </c>
     </row>
+    <row r="90" spans="1:10">
+      <c r="A90" t="s">
+        <v>133</v>
+      </c>
+      <c r="B90" t="s">
+        <v>134</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" t="s">
+        <v>114</v>
+      </c>
+      <c r="F90" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>13</v>
+      </c>
+      <c r="I90">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" t="s">
+        <v>135</v>
+      </c>
+      <c r="B91" t="s">
+        <v>136</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" t="s">
+        <v>114</v>
+      </c>
+      <c r="F91" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" t="s">
+        <v>13</v>
+      </c>
+      <c r="I91">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J91">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" t="s">
+        <v>137</v>
+      </c>
+      <c r="B92" t="s">
+        <v>138</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" t="s">
+        <v>7</v>
+      </c>
+      <c r="E92" t="s">
+        <v>114</v>
+      </c>
+      <c r="F92" t="s">
+        <v>22</v>
+      </c>
+      <c r="G92" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" t="s">
+        <v>13</v>
+      </c>
+      <c r="I92">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" t="s">
+        <v>139</v>
+      </c>
+      <c r="B93" t="s">
+        <v>140</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" t="s">
+        <v>7</v>
+      </c>
+      <c r="E93" t="s">
+        <v>114</v>
+      </c>
+      <c r="F93" t="s">
+        <v>27</v>
+      </c>
+      <c r="G93" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" t="s">
+        <v>13</v>
+      </c>
+      <c r="I93">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" t="s">
+        <v>141</v>
+      </c>
+      <c r="B94" t="s">
+        <v>142</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" t="s">
+        <v>7</v>
+      </c>
+      <c r="E94" t="s">
+        <v>114</v>
+      </c>
+      <c r="F94" t="s">
+        <v>27</v>
+      </c>
+      <c r="G94" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" t="s">
+        <v>13</v>
+      </c>
+      <c r="I94">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" t="s">
+        <v>143</v>
+      </c>
+      <c r="B95" t="s">
+        <v>144</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" t="s">
+        <v>114</v>
+      </c>
+      <c r="F95" t="s">
+        <v>9</v>
+      </c>
+      <c r="G95" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" t="s">
+        <v>145</v>
+      </c>
+      <c r="B96" t="s">
+        <v>146</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" t="s">
+        <v>114</v>
+      </c>
+      <c r="F96" t="s">
+        <v>9</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>13</v>
+      </c>
+      <c r="I96">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" t="s">
+        <v>147</v>
+      </c>
+      <c r="B97" t="s">
+        <v>148</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" t="s">
+        <v>7</v>
+      </c>
+      <c r="E97" t="s">
+        <v>114</v>
+      </c>
+      <c r="F97" t="s">
+        <v>36</v>
+      </c>
+      <c r="G97" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" t="s">
+        <v>150</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" t="s">
+        <v>114</v>
+      </c>
+      <c r="F98" t="s">
+        <v>36</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" t="s">
+        <v>151</v>
+      </c>
+      <c r="B99" t="s">
+        <v>152</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" t="s">
+        <v>114</v>
+      </c>
+      <c r="F99" t="s">
+        <v>41</v>
+      </c>
+      <c r="G99" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" t="s">
+        <v>153</v>
+      </c>
+      <c r="B100" t="s">
+        <v>154</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" t="s">
+        <v>114</v>
+      </c>
+      <c r="F100" t="s">
+        <v>41</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" t="s">
+        <v>155</v>
+      </c>
+      <c r="B101" t="s">
+        <v>156</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" t="s">
+        <v>114</v>
+      </c>
+      <c r="F101" t="s">
+        <v>46</v>
+      </c>
+      <c r="G101" t="s">
+        <v>13</v>
+      </c>
+      <c r="H101" t="s">
+        <v>13</v>
+      </c>
+      <c r="I101">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" t="s">
+        <v>157</v>
+      </c>
+      <c r="B102" t="s">
+        <v>158</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" t="s">
+        <v>114</v>
+      </c>
+      <c r="F102" t="s">
+        <v>46</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J102">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" t="s">
+        <v>159</v>
+      </c>
+      <c r="B103" t="s">
+        <v>160</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" t="s">
+        <v>114</v>
+      </c>
+      <c r="F103" t="s">
+        <v>51</v>
+      </c>
+      <c r="G103" t="s">
+        <v>13</v>
+      </c>
+      <c r="H103" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" t="s">
+        <v>161</v>
+      </c>
+      <c r="B104" t="s">
+        <v>162</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+      <c r="D104" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" t="s">
+        <v>114</v>
+      </c>
+      <c r="F104" t="s">
+        <v>51</v>
+      </c>
+      <c r="G104" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" t="s">
+        <v>163</v>
+      </c>
+      <c r="B105" t="s">
+        <v>164</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+      <c r="D105" t="s">
+        <v>7</v>
+      </c>
+      <c r="E105" t="s">
+        <v>114</v>
+      </c>
+      <c r="F105" t="s">
+        <v>56</v>
+      </c>
+      <c r="G105" t="s">
+        <v>13</v>
+      </c>
+      <c r="H105" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" t="s">
+        <v>165</v>
+      </c>
+      <c r="B106" t="s">
+        <v>166</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" t="s">
+        <v>114</v>
+      </c>
+      <c r="F106" t="s">
+        <v>56</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J106">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" t="s">
+        <v>167</v>
+      </c>
+      <c r="B107" t="s">
+        <v>168</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" t="s">
+        <v>114</v>
+      </c>
+      <c r="F107" t="s">
+        <v>61</v>
+      </c>
+      <c r="G107" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" t="s">
+        <v>169</v>
+      </c>
+      <c r="B108" t="s">
+        <v>170</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" t="s">
+        <v>7</v>
+      </c>
+      <c r="E108" t="s">
+        <v>114</v>
+      </c>
+      <c r="F108" t="s">
+        <v>61</v>
+      </c>
+      <c r="G108" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" t="s">
+        <v>171</v>
+      </c>
+      <c r="B109" t="s">
+        <v>172</v>
+      </c>
+      <c r="C109" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" t="s">
+        <v>7</v>
+      </c>
+      <c r="E109" t="s">
+        <v>114</v>
+      </c>
+      <c r="F109" t="s">
+        <v>66</v>
+      </c>
+      <c r="G109" t="s">
+        <v>13</v>
+      </c>
+      <c r="H109" t="s">
+        <v>13</v>
+      </c>
+      <c r="I109">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" t="s">
+        <v>173</v>
+      </c>
+      <c r="B110" t="s">
+        <v>174</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" t="s">
+        <v>7</v>
+      </c>
+      <c r="E110" t="s">
+        <v>114</v>
+      </c>
+      <c r="F110" t="s">
+        <v>66</v>
+      </c>
+      <c r="G110" t="s">
+        <v>19</v>
+      </c>
+      <c r="H110" t="s">
+        <v>13</v>
+      </c>
+      <c r="I110">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" t="s">
+        <v>175</v>
+      </c>
+      <c r="B111" t="s">
+        <v>176</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" t="s">
+        <v>7</v>
+      </c>
+      <c r="E111" t="s">
+        <v>114</v>
+      </c>
+      <c r="F111" t="s">
+        <v>71</v>
+      </c>
+      <c r="G111" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" t="s">
+        <v>13</v>
+      </c>
+      <c r="I111">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" t="s">
+        <v>177</v>
+      </c>
+      <c r="B112" t="s">
+        <v>178</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" t="s">
+        <v>7</v>
+      </c>
+      <c r="E112" t="s">
+        <v>114</v>
+      </c>
+      <c r="F112" t="s">
+        <v>71</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" t="s">
+        <v>179</v>
+      </c>
+      <c r="B113" t="s">
+        <v>180</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" t="s">
+        <v>7</v>
+      </c>
+      <c r="E113" t="s">
+        <v>119</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" t="s">
+        <v>181</v>
+      </c>
+      <c r="B114" t="s">
+        <v>182</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" t="s">
+        <v>7</v>
+      </c>
+      <c r="E114" t="s">
+        <v>119</v>
+      </c>
+      <c r="F114" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" t="s">
+        <v>13</v>
+      </c>
+      <c r="I114">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" t="s">
+        <v>183</v>
+      </c>
+      <c r="B115" t="s">
+        <v>184</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" t="s">
+        <v>7</v>
+      </c>
+      <c r="E115" t="s">
+        <v>119</v>
+      </c>
+      <c r="F115" t="s">
+        <v>80</v>
+      </c>
+      <c r="G115" t="s">
+        <v>13</v>
+      </c>
+      <c r="H115" t="s">
+        <v>13</v>
+      </c>
+      <c r="I115">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" t="s">
+        <v>185</v>
+      </c>
+      <c r="B116" t="s">
+        <v>186</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" t="s">
+        <v>7</v>
+      </c>
+      <c r="E116" t="s">
+        <v>119</v>
+      </c>
+      <c r="F116" t="s">
+        <v>80</v>
+      </c>
+      <c r="G116" t="s">
+        <v>19</v>
+      </c>
+      <c r="H116" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" t="s">
+        <v>187</v>
+      </c>
+      <c r="B117" t="s">
+        <v>188</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" t="s">
+        <v>7</v>
+      </c>
+      <c r="E117" t="s">
+        <v>119</v>
+      </c>
+      <c r="F117" t="s">
+        <v>85</v>
+      </c>
+      <c r="G117" t="s">
+        <v>13</v>
+      </c>
+      <c r="H117" t="s">
+        <v>13</v>
+      </c>
+      <c r="I117">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" t="s">
+        <v>189</v>
+      </c>
+      <c r="B118" t="s">
+        <v>190</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" t="s">
+        <v>7</v>
+      </c>
+      <c r="E118" t="s">
+        <v>119</v>
+      </c>
+      <c r="F118" t="s">
+        <v>85</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" t="s">
+        <v>191</v>
+      </c>
+      <c r="B119" t="s">
+        <v>192</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" t="s">
+        <v>7</v>
+      </c>
+      <c r="E119" t="s">
+        <v>119</v>
+      </c>
+      <c r="F119" t="s">
+        <v>90</v>
+      </c>
+      <c r="G119" t="s">
+        <v>13</v>
+      </c>
+      <c r="H119" t="s">
+        <v>13</v>
+      </c>
+      <c r="I119">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" t="s">
+        <v>193</v>
+      </c>
+      <c r="B120" t="s">
+        <v>194</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" t="s">
+        <v>7</v>
+      </c>
+      <c r="E120" t="s">
+        <v>119</v>
+      </c>
+      <c r="F120" t="s">
+        <v>90</v>
+      </c>
+      <c r="G120" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" t="s">
+        <v>195</v>
+      </c>
+      <c r="B121" t="s">
+        <v>196</v>
+      </c>
+      <c r="C121" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" t="s">
+        <v>7</v>
+      </c>
+      <c r="E121" t="s">
+        <v>119</v>
+      </c>
+      <c r="F121" t="s">
+        <v>95</v>
+      </c>
+      <c r="G121" t="s">
+        <v>13</v>
+      </c>
+      <c r="H121" t="s">
+        <v>13</v>
+      </c>
+      <c r="I121">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" t="s">
+        <v>197</v>
+      </c>
+      <c r="B122" t="s">
+        <v>198</v>
+      </c>
+      <c r="C122" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" t="s">
+        <v>7</v>
+      </c>
+      <c r="E122" t="s">
+        <v>119</v>
+      </c>
+      <c r="F122" t="s">
+        <v>95</v>
+      </c>
+      <c r="G122" t="s">
+        <v>19</v>
+      </c>
+      <c r="H122" t="s">
+        <v>13</v>
+      </c>
+      <c r="I122">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" t="s">
+        <v>199</v>
+      </c>
+      <c r="B123" t="s">
+        <v>200</v>
+      </c>
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" t="s">
+        <v>7</v>
+      </c>
+      <c r="E123" t="s">
+        <v>119</v>
+      </c>
+      <c r="F123" t="s">
+        <v>100</v>
+      </c>
+      <c r="G123" t="s">
+        <v>13</v>
+      </c>
+      <c r="H123" t="s">
+        <v>13</v>
+      </c>
+      <c r="I123">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" t="s">
+        <v>201</v>
+      </c>
+      <c r="B124" t="s">
+        <v>202</v>
+      </c>
+      <c r="C124" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" t="s">
+        <v>7</v>
+      </c>
+      <c r="E124" t="s">
+        <v>119</v>
+      </c>
+      <c r="F124" t="s">
+        <v>100</v>
+      </c>
+      <c r="G124" t="s">
+        <v>19</v>
+      </c>
+      <c r="H124" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J124">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" t="s">
+        <v>203</v>
+      </c>
+      <c r="B125" t="s">
+        <v>204</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" t="s">
+        <v>7</v>
+      </c>
+      <c r="E125" t="s">
+        <v>119</v>
+      </c>
+      <c r="F125" t="s">
+        <v>7</v>
+      </c>
+      <c r="G125" t="s">
+        <v>13</v>
+      </c>
+      <c r="H125" t="s">
+        <v>13</v>
+      </c>
+      <c r="I125">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" t="s">
+        <v>205</v>
+      </c>
+      <c r="B126" t="s">
+        <v>206</v>
+      </c>
+      <c r="C126" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" t="s">
+        <v>7</v>
+      </c>
+      <c r="E126" t="s">
+        <v>119</v>
+      </c>
+      <c r="F126" t="s">
+        <v>7</v>
+      </c>
+      <c r="G126" t="s">
+        <v>19</v>
+      </c>
+      <c r="H126" t="s">
+        <v>13</v>
+      </c>
+      <c r="I126">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J126">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
+      <c r="A127" t="s">
+        <v>207</v>
+      </c>
+      <c r="B127" t="s">
+        <v>208</v>
+      </c>
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" t="s">
+        <v>7</v>
+      </c>
+      <c r="E127" t="s">
+        <v>119</v>
+      </c>
+      <c r="F127" t="s">
+        <v>109</v>
+      </c>
+      <c r="G127" t="s">
+        <v>13</v>
+      </c>
+      <c r="H127" t="s">
+        <v>13</v>
+      </c>
+      <c r="I127">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J127">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
+      <c r="A128" t="s">
+        <v>209</v>
+      </c>
+      <c r="B128" t="s">
+        <v>210</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>7</v>
+      </c>
+      <c r="E128" t="s">
+        <v>119</v>
+      </c>
+      <c r="F128" t="s">
+        <v>109</v>
+      </c>
+      <c r="G128" t="s">
+        <v>19</v>
+      </c>
+      <c r="H128" t="s">
+        <v>13</v>
+      </c>
+      <c r="I128">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J128">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" t="s">
+        <v>211</v>
+      </c>
+      <c r="B129" t="s">
+        <v>212</v>
+      </c>
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" t="s">
+        <v>7</v>
+      </c>
+      <c r="E129" t="s">
+        <v>119</v>
+      </c>
+      <c r="F129" t="s">
+        <v>114</v>
+      </c>
+      <c r="G129" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" t="s">
+        <v>13</v>
+      </c>
+      <c r="I129">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" t="s">
+        <v>213</v>
+      </c>
+      <c r="B130" t="s">
+        <v>214</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" t="s">
+        <v>7</v>
+      </c>
+      <c r="E130" t="s">
+        <v>119</v>
+      </c>
+      <c r="F130" t="s">
+        <v>114</v>
+      </c>
+      <c r="G130" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" t="s">
+        <v>13</v>
+      </c>
+      <c r="I130">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J130">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" t="s">
+        <v>215</v>
+      </c>
+      <c r="B131" t="s">
+        <v>216</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" t="s">
+        <v>7</v>
+      </c>
+      <c r="E131" t="s">
+        <v>119</v>
+      </c>
+      <c r="F131" t="s">
+        <v>119</v>
+      </c>
+      <c r="G131" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" t="s">
+        <v>13</v>
+      </c>
+      <c r="I131">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J131">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" t="s">
+        <v>217</v>
+      </c>
+      <c r="B132" t="s">
+        <v>218</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" t="s">
+        <v>7</v>
+      </c>
+      <c r="E132" t="s">
+        <v>119</v>
+      </c>
+      <c r="F132" t="s">
+        <v>119</v>
+      </c>
+      <c r="G132" t="s">
+        <v>19</v>
+      </c>
+      <c r="H132" t="s">
+        <v>13</v>
+      </c>
+      <c r="I132">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J132">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" t="s">
+        <v>219</v>
+      </c>
+      <c r="B133" t="s">
+        <v>220</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" t="s">
+        <v>7</v>
+      </c>
+      <c r="E133" t="s">
+        <v>119</v>
+      </c>
+      <c r="F133" t="s">
+        <v>19</v>
+      </c>
+      <c r="G133" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" t="s">
+        <v>13</v>
+      </c>
+      <c r="I133">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" t="s">
+        <v>221</v>
+      </c>
+      <c r="B134" t="s">
+        <v>222</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" t="s">
+        <v>7</v>
+      </c>
+      <c r="E134" t="s">
+        <v>119</v>
+      </c>
+      <c r="F134" t="s">
+        <v>19</v>
+      </c>
+      <c r="G134" t="s">
+        <v>19</v>
+      </c>
+      <c r="H134" t="s">
+        <v>13</v>
+      </c>
+      <c r="I134">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J134">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" t="s">
+        <v>223</v>
+      </c>
+      <c r="B135" t="s">
+        <v>224</v>
+      </c>
+      <c r="C135" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" t="s">
+        <v>7</v>
+      </c>
+      <c r="E135" t="s">
+        <v>119</v>
+      </c>
+      <c r="F135" t="s">
+        <v>128</v>
+      </c>
+      <c r="G135" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" t="s">
+        <v>13</v>
+      </c>
+      <c r="I135">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J135">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" t="s">
+        <v>225</v>
+      </c>
+      <c r="B136" t="s">
+        <v>226</v>
+      </c>
+      <c r="C136" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" t="s">
+        <v>7</v>
+      </c>
+      <c r="E136" t="s">
+        <v>119</v>
+      </c>
+      <c r="F136" t="s">
+        <v>128</v>
+      </c>
+      <c r="G136" t="s">
+        <v>19</v>
+      </c>
+      <c r="H136" t="s">
+        <v>13</v>
+      </c>
+      <c r="I136">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J136">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" t="s">
+        <v>227</v>
+      </c>
+      <c r="B137" t="s">
+        <v>228</v>
+      </c>
+      <c r="C137" t="s">
+        <v>5</v>
+      </c>
+      <c r="D137" t="s">
+        <v>7</v>
+      </c>
+      <c r="E137" t="s">
+        <v>119</v>
+      </c>
+      <c r="F137" t="s">
+        <v>11</v>
+      </c>
+      <c r="G137" t="s">
+        <v>13</v>
+      </c>
+      <c r="H137" t="s">
+        <v>13</v>
+      </c>
+      <c r="I137">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" t="s">
+        <v>229</v>
+      </c>
+      <c r="B138" t="s">
+        <v>230</v>
+      </c>
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>7</v>
+      </c>
+      <c r="E138" t="s">
+        <v>119</v>
+      </c>
+      <c r="F138" t="s">
+        <v>11</v>
+      </c>
+      <c r="G138" t="s">
+        <v>19</v>
+      </c>
+      <c r="H138" t="s">
+        <v>13</v>
+      </c>
+      <c r="I138">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J138">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" t="s">
+        <v>231</v>
+      </c>
+      <c r="B139" t="s">
+        <v>232</v>
+      </c>
+      <c r="C139" t="s">
+        <v>5</v>
+      </c>
+      <c r="D139" t="s">
+        <v>7</v>
+      </c>
+      <c r="E139" t="s">
+        <v>119</v>
+      </c>
+      <c r="F139" t="s">
+        <v>22</v>
+      </c>
+      <c r="G139" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" t="s">
+        <v>13</v>
+      </c>
+      <c r="I139">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" t="s">
+        <v>233</v>
+      </c>
+      <c r="B140" t="s">
+        <v>234</v>
+      </c>
+      <c r="C140" t="s">
+        <v>5</v>
+      </c>
+      <c r="D140" t="s">
+        <v>7</v>
+      </c>
+      <c r="E140" t="s">
+        <v>119</v>
+      </c>
+      <c r="F140" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140" t="s">
+        <v>19</v>
+      </c>
+      <c r="H140" t="s">
+        <v>13</v>
+      </c>
+      <c r="I140">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J140">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" t="s">
+        <v>235</v>
+      </c>
+      <c r="B141" t="s">
+        <v>236</v>
+      </c>
+      <c r="C141" t="s">
+        <v>5</v>
+      </c>
+      <c r="D141" t="s">
+        <v>7</v>
+      </c>
+      <c r="E141" t="s">
+        <v>119</v>
+      </c>
+      <c r="F141" t="s">
+        <v>27</v>
+      </c>
+      <c r="G141" t="s">
+        <v>13</v>
+      </c>
+      <c r="H141" t="s">
+        <v>13</v>
+      </c>
+      <c r="I141">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142" t="s">
+        <v>237</v>
+      </c>
+      <c r="B142" t="s">
+        <v>238</v>
+      </c>
+      <c r="C142" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" t="s">
+        <v>7</v>
+      </c>
+      <c r="E142" t="s">
+        <v>119</v>
+      </c>
+      <c r="F142" t="s">
+        <v>27</v>
+      </c>
+      <c r="G142" t="s">
+        <v>19</v>
+      </c>
+      <c r="H142" t="s">
+        <v>13</v>
+      </c>
+      <c r="I142">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J142">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" t="s">
+        <v>239</v>
+      </c>
+      <c r="B143" t="s">
+        <v>240</v>
+      </c>
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>7</v>
+      </c>
+      <c r="E143" t="s">
+        <v>119</v>
+      </c>
+      <c r="F143" t="s">
+        <v>9</v>
+      </c>
+      <c r="G143" t="s">
+        <v>13</v>
+      </c>
+      <c r="H143" t="s">
+        <v>13</v>
+      </c>
+      <c r="I143">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144" t="s">
+        <v>241</v>
+      </c>
+      <c r="B144" t="s">
+        <v>242</v>
+      </c>
+      <c r="C144" t="s">
+        <v>5</v>
+      </c>
+      <c r="D144" t="s">
+        <v>7</v>
+      </c>
+      <c r="E144" t="s">
+        <v>119</v>
+      </c>
+      <c r="F144" t="s">
+        <v>9</v>
+      </c>
+      <c r="G144" t="s">
+        <v>19</v>
+      </c>
+      <c r="H144" t="s">
+        <v>13</v>
+      </c>
+      <c r="I144">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J144">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" t="s">
+        <v>243</v>
+      </c>
+      <c r="B145" t="s">
+        <v>244</v>
+      </c>
+      <c r="C145" t="s">
+        <v>5</v>
+      </c>
+      <c r="D145" t="s">
+        <v>7</v>
+      </c>
+      <c r="E145" t="s">
+        <v>119</v>
+      </c>
+      <c r="F145" t="s">
+        <v>36</v>
+      </c>
+      <c r="G145" t="s">
+        <v>13</v>
+      </c>
+      <c r="H145" t="s">
+        <v>13</v>
+      </c>
+      <c r="I145">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" t="s">
+        <v>245</v>
+      </c>
+      <c r="B146" t="s">
+        <v>246</v>
+      </c>
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" t="s">
+        <v>7</v>
+      </c>
+      <c r="E146" t="s">
+        <v>119</v>
+      </c>
+      <c r="F146" t="s">
+        <v>36</v>
+      </c>
+      <c r="G146" t="s">
+        <v>19</v>
+      </c>
+      <c r="H146" t="s">
+        <v>13</v>
+      </c>
+      <c r="I146">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" t="s">
+        <v>247</v>
+      </c>
+      <c r="B147" t="s">
+        <v>248</v>
+      </c>
+      <c r="C147" t="s">
+        <v>5</v>
+      </c>
+      <c r="D147" t="s">
+        <v>7</v>
+      </c>
+      <c r="E147" t="s">
+        <v>119</v>
+      </c>
+      <c r="F147" t="s">
+        <v>41</v>
+      </c>
+      <c r="G147" t="s">
+        <v>13</v>
+      </c>
+      <c r="H147" t="s">
+        <v>13</v>
+      </c>
+      <c r="I147">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J147">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" t="s">
+        <v>249</v>
+      </c>
+      <c r="B148" t="s">
+        <v>250</v>
+      </c>
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+      <c r="D148" t="s">
+        <v>7</v>
+      </c>
+      <c r="E148" t="s">
+        <v>119</v>
+      </c>
+      <c r="F148" t="s">
+        <v>41</v>
+      </c>
+      <c r="G148" t="s">
+        <v>19</v>
+      </c>
+      <c r="H148" t="s">
+        <v>13</v>
+      </c>
+      <c r="I148">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149" t="s">
+        <v>251</v>
+      </c>
+      <c r="B149" t="s">
+        <v>252</v>
+      </c>
+      <c r="C149" t="s">
+        <v>5</v>
+      </c>
+      <c r="D149" t="s">
+        <v>7</v>
+      </c>
+      <c r="E149" t="s">
+        <v>119</v>
+      </c>
+      <c r="F149" t="s">
+        <v>46</v>
+      </c>
+      <c r="G149" t="s">
+        <v>13</v>
+      </c>
+      <c r="H149" t="s">
+        <v>13</v>
+      </c>
+      <c r="I149">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" t="s">
+        <v>253</v>
+      </c>
+      <c r="B150" t="s">
+        <v>254</v>
+      </c>
+      <c r="C150" t="s">
+        <v>5</v>
+      </c>
+      <c r="D150" t="s">
+        <v>7</v>
+      </c>
+      <c r="E150" t="s">
+        <v>119</v>
+      </c>
+      <c r="F150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G150" t="s">
+        <v>19</v>
+      </c>
+      <c r="H150" t="s">
+        <v>13</v>
+      </c>
+      <c r="I150">
+        <v>1800.0106666666666</v>
+      </c>
+      <c r="J150">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151" t="s">
+        <v>255</v>
+      </c>
+      <c r="B151" t="s">
+        <v>256</v>
+      </c>
+      <c r="C151" t="s">
+        <v>5</v>
+      </c>
+      <c r="D151" t="s">
+        <v>7</v>
+      </c>
+      <c r="E151" t="s">
+        <v>119</v>
+      </c>
+      <c r="F151" t="s">
+        <v>51</v>
+      </c>
+      <c r="G151" t="s">
+        <v>13</v>
+      </c>
+      <c r="H151" t="s">
+        <v>13</v>
+      </c>
+      <c r="I151">
+        <v>120.00133333333333</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
